--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.5506,0.3248,0.0349,0.1196</t>
-  </si>
-  <si>
-    <t>0.0693,0.0039,0.0034,0.9709</t>
-  </si>
-  <si>
-    <t>0.7061,0.1416,0.0228,0.1137</t>
-  </si>
-  <si>
-    <t>0.0656,0.0044,0.0010,0.9828</t>
-  </si>
-  <si>
-    <t>0.9972,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0040,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9888,0.0051,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9957,0.0007,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9932,0.0010,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9950,0.0019,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9969,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0018,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.3823,0.4987,0.0626,0.1157</t>
-  </si>
-  <si>
-    <t>0.1057,0.0370,0.8858,0.0017</t>
-  </si>
-  <si>
-    <t>0.1239,0.0389,0.8720,0.0070</t>
-  </si>
-  <si>
-    <t>0.3134,0.0937,0.6355,0.1258</t>
-  </si>
-  <si>
-    <t>0.7296,0.1228,0.1834,0.0217</t>
-  </si>
-  <si>
-    <t>0.0097,0.9834,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.0745,0.9396,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.4767,0.6174,0.0209,0.0013</t>
-  </si>
-  <si>
-    <t>0.0948,0.9251,0.0063,0.0007</t>
-  </si>
-  <si>
-    <t>0.0153,0.9824,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.6379,0.0036,0.2211,0.1021</t>
-  </si>
-  <si>
-    <t>0.5931,0.0635,0.3539,0.0714</t>
-  </si>
-  <si>
-    <t>0.1151,0.0031,0.9295,0.0104</t>
-  </si>
-  <si>
-    <t>0.2127,0.0054,0.8891,0.0049</t>
-  </si>
-  <si>
-    <t>0.0499,0.0053,0.9607,0.0048</t>
-  </si>
-  <si>
-    <t>0.1913,0.0111,0.8806,0.0049</t>
-  </si>
-  <si>
-    <t>0.0068,0.0031,0.9839,0.0114</t>
-  </si>
-  <si>
-    <t>0.5711,0.5570,0.0087,0.0057</t>
-  </si>
-  <si>
-    <t>0.3825,0.4676,0.1920,0.0019</t>
-  </si>
-  <si>
-    <t>0.0035,0.0162,0.9846,0.0059</t>
-  </si>
-  <si>
-    <t>0.1119,0.8240,0.0790,0.0005</t>
-  </si>
-  <si>
-    <t>0.6454,0.3415,0.0216,0.0280</t>
-  </si>
-  <si>
-    <t>0.0822,0.5503,0.5448,0.0011</t>
-  </si>
-  <si>
-    <t>0.4076,0.6964,0.0145,0.0008</t>
-  </si>
-  <si>
-    <t>0.1696,0.8642,0.0344,0.0031</t>
-  </si>
-  <si>
-    <t>0.0195,0.3950,0.4807,0.0866</t>
-  </si>
-  <si>
-    <t>0.0143,0.0353,0.9611,0.0151</t>
-  </si>
-  <si>
-    <t>0.1152,0.1749,0.7310,0.0447</t>
-  </si>
-  <si>
-    <t>0.0449,0.0202,0.8822,0.0997</t>
-  </si>
-  <si>
-    <t>0.0255,0.2399,0.9088,0.0117</t>
-  </si>
-  <si>
-    <t>0.0139,0.9391,0.1132,0.0002</t>
-  </si>
-  <si>
-    <t>0.0172,0.0314,0.9629,0.0027</t>
-  </si>
-  <si>
-    <t>0.1008,0.5730,0.0145,0.6508</t>
-  </si>
-  <si>
-    <t>0.0025,0.9821,0.0033,0.0135</t>
-  </si>
-  <si>
-    <t>0.0024,0.9871,0.0150,0.0014</t>
-  </si>
-  <si>
-    <t>0.0015,0.9779,0.0125,0.0361</t>
-  </si>
-  <si>
-    <t>0.0052,0.0503,0.9761,0.0061</t>
-  </si>
-  <si>
-    <t>0.0001,0.0297,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0613,0.0043,0.9413,0.0198</t>
-  </si>
-  <si>
-    <t>0.1009,0.0070,0.9319,0.0053</t>
-  </si>
-  <si>
-    <t>0.0074,0.0120,0.9824,0.0077</t>
-  </si>
-  <si>
-    <t>0.0063,0.0333,0.9784,0.0005</t>
-  </si>
-  <si>
-    <t>0.9410,0.0686,0.0054,0.0036</t>
-  </si>
-  <si>
-    <t>0.9705,0.0080,0.0030,0.0064</t>
-  </si>
-  <si>
-    <t>0.9478,0.0511,0.0124,0.0020</t>
-  </si>
-  <si>
-    <t>0.0036,0.0511,0.9877,0.0015</t>
-  </si>
-  <si>
-    <t>0.9875,0.0045,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9900,0.0116,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9784,0.0178,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.0015,0.8908,0.9251,0.0003</t>
-  </si>
-  <si>
-    <t>0.0042,0.1104,0.9808,0.0021</t>
-  </si>
-  <si>
-    <t>0.0525,0.1254,0.9029,0.0044</t>
-  </si>
-  <si>
-    <t>0.0001,0.8996,0.9840,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0073,0.9942,0.0007</t>
-  </si>
-  <si>
-    <t>0.1097,0.7499,0.2998,0.0057</t>
-  </si>
-  <si>
-    <t>0.0425,0.9437,0.0112,0.0038</t>
-  </si>
-  <si>
-    <t>0.8565,0.0338,0.1498,0.0087</t>
-  </si>
-  <si>
-    <t>0.5320,0.1162,0.4282,0.0076</t>
-  </si>
-  <si>
-    <t>0.0028,0.0308,0.9897,0.0015</t>
-  </si>
-  <si>
-    <t>0.0060,0.8696,0.6612,0.0011</t>
-  </si>
-  <si>
-    <t>0.0099,0.8270,0.8077,0.0028</t>
-  </si>
-  <si>
-    <t>0.0002,0.9884,0.5254,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.8023,0.8885,0.0026</t>
-  </si>
-  <si>
-    <t>0.1667,0.0010,0.0056,0.9376</t>
-  </si>
-  <si>
-    <t>0.0098,0.0061,0.0006,0.9960</t>
-  </si>
-  <si>
-    <t>0.0289,0.0020,0.0036,0.9862</t>
-  </si>
-  <si>
-    <t>0.0096,0.0094,0.0063,0.9909</t>
-  </si>
-  <si>
-    <t>0.0369,0.0036,0.0048,0.9829</t>
-  </si>
-  <si>
-    <t>0.0062,0.0379,0.0011,0.9946</t>
-  </si>
-  <si>
-    <t>0.0004,0.9865,0.6811,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9008,0.9570,0.0002</t>
-  </si>
-  <si>
-    <t>0.0065,0.9378,0.0850,0.0107</t>
-  </si>
-  <si>
-    <t>0.0066,0.4933,0.8634,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.8774,0.9104,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.7766,0.8112,0.0008</t>
-  </si>
-  <si>
-    <t>0.9945,0.0038,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9737,0.0269,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9837,0.0155,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9952,0.0025,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9921,0.0049,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9916,0.0040,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9912,0.0050,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9851,0.0090,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9899,0.0053,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9948,0.0006,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9944,0.0071,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9960,0.0044,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0013,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9959,0.0006,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0081,0.0033,0.9615,0.0831</t>
-  </si>
-  <si>
-    <t>0.1856,0.0076,0.9012,0.0025</t>
-  </si>
-  <si>
-    <t>0.8324,0.0145,0.0902,0.0543</t>
-  </si>
-  <si>
-    <t>0.0093,0.0071,0.9827,0.0035</t>
-  </si>
-  <si>
-    <t>0.1428,0.8821,0.0108,0.0003</t>
-  </si>
-  <si>
-    <t>0.0184,0.9747,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.3033,0.7875,0.0017,0.0014</t>
-  </si>
-  <si>
-    <t>0.2793,0.7865,0.0031,0.0046</t>
-  </si>
-  <si>
-    <t>0.1144,0.9182,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.0146,0.9779,0.0101,0.0001</t>
-  </si>
-  <si>
-    <t>0.7464,0.3727,0.0064,0.0015</t>
-  </si>
-  <si>
-    <t>0.2279,0.6979,0.1545,0.0092</t>
-  </si>
-  <si>
-    <t>0.1604,0.0226,0.8740,0.0047</t>
-  </si>
-  <si>
-    <t>0.1689,0.7199,0.0586,0.0698</t>
-  </si>
-  <si>
-    <t>0.7025,0.0403,0.3698,0.0124</t>
-  </si>
-  <si>
-    <t>0.1239,0.4244,0.0504,0.7643</t>
-  </si>
-  <si>
-    <t>0.0023,0.9865,0.0119,0.0065</t>
-  </si>
-  <si>
-    <t>0.0630,0.8985,0.0520,0.0146</t>
-  </si>
-  <si>
-    <t>0.0145,0.9222,0.0102,0.0884</t>
-  </si>
-  <si>
-    <t>0.0035,0.9184,0.8398,0.0005</t>
-  </si>
-  <si>
-    <t>0.1205,0.9109,0.0217,0.0003</t>
-  </si>
-  <si>
-    <t>0.6845,0.3467,0.0250,0.0026</t>
-  </si>
-  <si>
-    <t>0.6603,0.4149,0.0240,0.0024</t>
-  </si>
-  <si>
-    <t>0.9718,0.0179,0.0045,0.0023</t>
-  </si>
-  <si>
-    <t>0.9881,0.0018,0.0003,0.0034</t>
-  </si>
-  <si>
-    <t>0.9871,0.0066,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9885,0.0031,0.0006,0.0023</t>
-  </si>
-  <si>
-    <t>0.9841,0.0043,0.0029,0.0029</t>
-  </si>
-  <si>
-    <t>0.9740,0.0094,0.0136,0.0023</t>
-  </si>
-  <si>
-    <t>0.9915,0.0017,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9937,0.0005,0.0000,0.0024</t>
-  </si>
-  <si>
-    <t>0.0066,0.5624,0.9334,0.0033</t>
-  </si>
-  <si>
-    <t>0.0029,0.8274,0.8807,0.0006</t>
-  </si>
-  <si>
-    <t>0.0028,0.1607,0.9829,0.0006</t>
-  </si>
-  <si>
-    <t>0.0197,0.2163,0.8524,0.0011</t>
-  </si>
-  <si>
-    <t>0.7489,0.0451,0.1273,0.0882</t>
-  </si>
-  <si>
-    <t>0.8043,0.0642,0.1698,0.0056</t>
-  </si>
-  <si>
-    <t>0.7514,0.0025,0.4624,0.0045</t>
-  </si>
-  <si>
-    <t>0.6799,0.1210,0.2372,0.0178</t>
-  </si>
-  <si>
-    <t>0.0351,0.0129,0.0037,0.9829</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.0020,0.9983</t>
-  </si>
-  <si>
-    <t>0.0041,0.0018,0.0011,0.9977</t>
-  </si>
-  <si>
-    <t>0.0441,0.0002,0.0262,0.9472</t>
-  </si>
-  <si>
-    <t>0.0016,0.8707,0.8878,0.0002</t>
-  </si>
-  <si>
-    <t>0.9859,0.0072,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.9159,0.0533,0.0072,0.0107</t>
-  </si>
-  <si>
-    <t>0.9759,0.0065,0.0022,0.0056</t>
-  </si>
-  <si>
-    <t>0.6919,0.4062,0.0128,0.0024</t>
-  </si>
-  <si>
-    <t>0.9828,0.0024,0.0034,0.0036</t>
-  </si>
-  <si>
-    <t>0.0588,0.5176,0.0227,0.8511</t>
-  </si>
-  <si>
-    <t>0.9689,0.0056,0.0013,0.0105</t>
-  </si>
-  <si>
-    <t>0.0021,0.4708,0.8870,0.0119</t>
-  </si>
-  <si>
-    <t>0.8586,0.0031,0.0513,0.0604</t>
-  </si>
-  <si>
-    <t>0.9481,0.0124,0.0178,0.0105</t>
-  </si>
-  <si>
-    <t>0.2068,0.7863,0.0148,0.0313</t>
-  </si>
-  <si>
-    <t>0.9009,0.0808,0.0171,0.0061</t>
-  </si>
-  <si>
-    <t>0.8947,0.0616,0.0312,0.0049</t>
-  </si>
-  <si>
-    <t>0.4453,0.5502,0.0176,0.0255</t>
-  </si>
-  <si>
-    <t>0.9004,0.1046,0.0120,0.0030</t>
-  </si>
-  <si>
-    <t>0.5270,0.5585,0.0287,0.0053</t>
-  </si>
-  <si>
-    <t>0.9800,0.0079,0.0005,0.0032</t>
-  </si>
-  <si>
-    <t>0.9854,0.0067,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.9894,0.0038,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.9913,0.0007,0.0003,0.0040</t>
-  </si>
-  <si>
-    <t>0.9873,0.0043,0.0018,0.0016</t>
-  </si>
-  <si>
-    <t>0.9864,0.0024,0.0008,0.0036</t>
-  </si>
-  <si>
-    <t>0.9917,0.0014,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.1661,0.8514,0.0078,0.0058</t>
-  </si>
-  <si>
-    <t>0.6626,0.4800,0.0097,0.0013</t>
-  </si>
-  <si>
-    <t>0.3660,0.7682,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.5317,0.3077,0.2272,0.0048</t>
-  </si>
-  <si>
-    <t>0.9385,0.1055,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9614,0.0338,0.0034,0.0017</t>
-  </si>
-  <si>
-    <t>0.9487,0.0163,0.0104,0.0121</t>
-  </si>
-  <si>
-    <t>0.9583,0.0326,0.0018,0.0026</t>
-  </si>
-  <si>
-    <t>0.0029,0.0316,0.9921,0.0008</t>
-  </si>
-  <si>
-    <t>0.8952,0.1382,0.0024,0.0023</t>
-  </si>
-  <si>
-    <t>0.0068,0.0044,0.9888,0.0010</t>
-  </si>
-  <si>
-    <t>0.0281,0.1700,0.9426,0.0057</t>
-  </si>
-  <si>
-    <t>0.0090,0.0030,0.9825,0.0100</t>
-  </si>
-  <si>
-    <t>0.0013,0.1318,0.9856,0.0007</t>
-  </si>
-  <si>
-    <t>0.0402,0.0118,0.9609,0.0032</t>
-  </si>
-  <si>
-    <t>0.0265,0.0029,0.9805,0.0017</t>
-  </si>
-  <si>
-    <t>0.0026,0.0043,0.9958,0.0002</t>
-  </si>
-  <si>
-    <t>0.0751,0.0279,0.9215,0.0068</t>
-  </si>
-  <si>
-    <t>0.2189,0.0707,0.7662,0.0226</t>
-  </si>
-  <si>
-    <t>0.4137,0.1295,0.5379,0.0927</t>
-  </si>
-  <si>
-    <t>0.4778,0.0796,0.4705,0.0037</t>
-  </si>
-  <si>
-    <t>0.4065,0.0536,0.6357,0.0085</t>
-  </si>
-  <si>
-    <t>0.2883,0.0894,0.6369,0.0145</t>
-  </si>
-  <si>
-    <t>0.7789,0.0727,0.1259,0.0138</t>
-  </si>
-  <si>
-    <t>0.3242,0.0467,0.7142,0.0212</t>
-  </si>
-  <si>
-    <t>0.5389,0.6299,0.0039,0.0007</t>
-  </si>
-  <si>
-    <t>0.8111,0.2623,0.0093,0.0010</t>
-  </si>
-  <si>
-    <t>0.9822,0.0126,0.0052,0.0008</t>
-  </si>
-  <si>
-    <t>0.9868,0.0115,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.7506,0.4376,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.7775,0.1180,0.1247,0.0187</t>
-  </si>
-  <si>
-    <t>0.6917,0.0394,0.3443,0.0215</t>
-  </si>
-  <si>
-    <t>0.3183,0.3084,0.3473,0.2878</t>
-  </si>
-  <si>
-    <t>0.8359,0.0063,0.2007,0.0140</t>
-  </si>
-  <si>
-    <t>0.7480,0.0340,0.1766,0.0671</t>
-  </si>
-  <si>
-    <t>0.0024,0.0027,0.9874,0.0181</t>
-  </si>
-  <si>
-    <t>0.0549,0.6733,0.6867,0.0300</t>
-  </si>
-  <si>
-    <t>0.0162,0.4407,0.8648,0.0031</t>
-  </si>
-  <si>
-    <t>0.0444,0.0513,0.9034,0.0376</t>
-  </si>
-  <si>
-    <t>0.0148,0.0292,0.9648,0.0033</t>
-  </si>
-  <si>
-    <t>0.9843,0.0093,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9913,0.0049,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9897,0.0065,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9912,0.0058,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9808,0.0179,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.9822,0.0125,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.9842,0.0166,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9901,0.0063,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0914,0.0197,0.9339,0.0061</t>
-  </si>
-  <si>
-    <t>0.2673,0.6122,0.1885,0.0158</t>
-  </si>
-  <si>
-    <t>0.4581,0.2538,0.1693,0.3710</t>
-  </si>
-  <si>
-    <t>0.0045,0.0219,0.9858,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0142,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0465,0.1378,0.7817,0.0114</t>
-  </si>
-  <si>
-    <t>0.0054,0.0039,0.9908,0.0024</t>
-  </si>
-  <si>
-    <t>0.1783,0.1821,0.6139,0.1874</t>
-  </si>
-  <si>
-    <t>0.0012,0.0156,0.9935,0.0010</t>
-  </si>
-  <si>
-    <t>0.0332,0.1144,0.9073,0.0060</t>
-  </si>
-  <si>
-    <t>0.1498,0.0725,0.8253,0.0145</t>
-  </si>
-  <si>
-    <t>0.7415,0.0086,0.3519,0.0157</t>
-  </si>
-  <si>
-    <t>0.8179,0.0018,0.2138,0.0141</t>
-  </si>
-  <si>
-    <t>0.7350,0.0279,0.0219,0.2379</t>
-  </si>
-  <si>
-    <t>0.9965,0.0012,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0028,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9938,0.0056,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9905,0.0038,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9923,0.0015,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9947,0.0028,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9887,0.0064,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9759,0.0260,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.0139,0.4257,0.7883,0.0013</t>
-  </si>
-  <si>
-    <t>0.0050,0.0361,0.9822,0.0017</t>
-  </si>
-  <si>
-    <t>0.0012,0.0060,0.9896,0.0091</t>
-  </si>
-  <si>
-    <t>0.1784,0.0310,0.8461,0.0059</t>
-  </si>
-  <si>
-    <t>0.0073,0.0043,0.9888,0.0022</t>
-  </si>
-  <si>
-    <t>0.2108,0.0222,0.4830,0.3405</t>
-  </si>
-  <si>
-    <t>0.0280,0.0130,0.9524,0.0146</t>
-  </si>
-  <si>
-    <t>0.0101,0.0089,0.9542,0.0635</t>
-  </si>
-  <si>
-    <t>0.4144,0.0007,0.0009,0.8581</t>
-  </si>
-  <si>
-    <t>0.0081,0.1822,0.0084,0.9822</t>
-  </si>
-  <si>
-    <t>0.0196,0.0027,0.0005,0.9940</t>
-  </si>
-  <si>
-    <t>0.0035,0.0004,0.0032,0.9963</t>
-  </si>
-  <si>
-    <t>0.0030,0.0003,0.0022,0.9974</t>
-  </si>
-  <si>
-    <t>0.3792,0.3093,0.0214,0.2887</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.6305,0.2870,0.0157,0.0370</t>
+  </si>
+  <si>
+    <t>0.0480,0.0100,0.0026,0.9836</t>
+  </si>
+  <si>
+    <t>0.7854,0.0167,0.0172,0.1884</t>
+  </si>
+  <si>
+    <t>0.0453,0.0045,0.0006,0.9889</t>
+  </si>
+  <si>
+    <t>0.9964,0.0023,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0038,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0032,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0023,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0029,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0019,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0023,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.7406,0.1658,0.1543,0.0156</t>
+  </si>
+  <si>
+    <t>0.4224,0.0216,0.7357,0.0041</t>
+  </si>
+  <si>
+    <t>0.4226,0.0392,0.6562,0.0028</t>
+  </si>
+  <si>
+    <t>0.0589,0.0127,0.9285,0.0129</t>
+  </si>
+  <si>
+    <t>0.4402,0.1862,0.4839,0.0244</t>
+  </si>
+  <si>
+    <t>0.0606,0.9433,0.0086,0.0012</t>
+  </si>
+  <si>
+    <t>0.0762,0.9403,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.4686,0.6901,0.0044,0.0010</t>
+  </si>
+  <si>
+    <t>0.1392,0.8930,0.0020,0.0020</t>
+  </si>
+  <si>
+    <t>0.0761,0.9367,0.0089,0.0005</t>
+  </si>
+  <si>
+    <t>0.5788,0.0055,0.1344,0.2463</t>
+  </si>
+  <si>
+    <t>0.7496,0.0059,0.2926,0.0155</t>
+  </si>
+  <si>
+    <t>0.1154,0.0122,0.8591,0.0406</t>
+  </si>
+  <si>
+    <t>0.0770,0.0194,0.8925,0.0323</t>
+  </si>
+  <si>
+    <t>0.2956,0.0181,0.8249,0.0078</t>
+  </si>
+  <si>
+    <t>0.0546,0.0045,0.9362,0.0378</t>
+  </si>
+  <si>
+    <t>0.0014,0.0016,0.9884,0.0217</t>
+  </si>
+  <si>
+    <t>0.3448,0.7533,0.0110,0.0063</t>
+  </si>
+  <si>
+    <t>0.6932,0.2213,0.1342,0.0104</t>
+  </si>
+  <si>
+    <t>0.0004,0.0092,0.9954,0.0019</t>
+  </si>
+  <si>
+    <t>0.0476,0.8880,0.1445,0.0017</t>
+  </si>
+  <si>
+    <t>0.8518,0.0484,0.0088,0.0618</t>
+  </si>
+  <si>
+    <t>0.5394,0.1357,0.3857,0.0301</t>
+  </si>
+  <si>
+    <t>0.5515,0.5133,0.0323,0.0018</t>
+  </si>
+  <si>
+    <t>0.0963,0.8983,0.0631,0.0016</t>
+  </si>
+  <si>
+    <t>0.0806,0.3509,0.4087,0.0397</t>
+  </si>
+  <si>
+    <t>0.0014,0.0037,0.9903,0.0161</t>
+  </si>
+  <si>
+    <t>0.0932,0.1061,0.7628,0.0818</t>
+  </si>
+  <si>
+    <t>0.0313,0.1322,0.9039,0.0145</t>
+  </si>
+  <si>
+    <t>0.0323,0.5297,0.7033,0.0082</t>
+  </si>
+  <si>
+    <t>0.0091,0.9399,0.1520,0.0015</t>
+  </si>
+  <si>
+    <t>0.0191,0.0184,0.9660,0.0041</t>
+  </si>
+  <si>
+    <t>0.0751,0.6764,0.0343,0.6297</t>
+  </si>
+  <si>
+    <t>0.0051,0.9832,0.0028,0.0066</t>
+  </si>
+  <si>
+    <t>0.0118,0.9446,0.1689,0.0082</t>
+  </si>
+  <si>
+    <t>0.0009,0.9865,0.0119,0.0139</t>
+  </si>
+  <si>
+    <t>0.0124,0.1026,0.9384,0.0200</t>
+  </si>
+  <si>
+    <t>0.0014,0.0701,0.9855,0.0018</t>
+  </si>
+  <si>
+    <t>0.0329,0.0077,0.9498,0.0298</t>
+  </si>
+  <si>
+    <t>0.3637,0.0054,0.7500,0.0165</t>
+  </si>
+  <si>
+    <t>0.0018,0.0106,0.9922,0.0024</t>
+  </si>
+  <si>
+    <t>0.0027,0.0032,0.9938,0.0006</t>
+  </si>
+  <si>
+    <t>0.8511,0.2379,0.0039,0.0015</t>
+  </si>
+  <si>
+    <t>0.9820,0.0112,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9216,0.0794,0.0163,0.0041</t>
+  </si>
+  <si>
+    <t>0.0035,0.0137,0.9899,0.0065</t>
+  </si>
+  <si>
+    <t>0.9879,0.0091,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9918,0.0043,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9516,0.0635,0.0087,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.8132,0.9746,0.0003</t>
+  </si>
+  <si>
+    <t>0.0292,0.1254,0.9369,0.0035</t>
+  </si>
+  <si>
+    <t>0.0301,0.0432,0.8134,0.1144</t>
+  </si>
+  <si>
+    <t>0.0003,0.9202,0.9689,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9986,0.0012</t>
+  </si>
+  <si>
+    <t>0.0446,0.8927,0.1488,0.0008</t>
+  </si>
+  <si>
+    <t>0.0236,0.9686,0.0090,0.0010</t>
+  </si>
+  <si>
+    <t>0.6247,0.0492,0.4313,0.0149</t>
+  </si>
+  <si>
+    <t>0.5960,0.0994,0.4516,0.0054</t>
+  </si>
+  <si>
+    <t>0.0036,0.0830,0.9873,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.9542,0.7304,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.8642,0.8494,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9831,0.7889,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.8783,0.9599,0.0002</t>
+  </si>
+  <si>
+    <t>0.0406,0.0006,0.0467,0.9450</t>
+  </si>
+  <si>
+    <t>0.0046,0.0072,0.0042,0.9960</t>
+  </si>
+  <si>
+    <t>0.0066,0.0008,0.0005,0.9973</t>
+  </si>
+  <si>
+    <t>0.0095,0.0931,0.0057,0.9888</t>
+  </si>
+  <si>
+    <t>0.0343,0.0020,0.0142,0.9753</t>
+  </si>
+  <si>
+    <t>0.0057,0.0119,0.0007,0.9963</t>
+  </si>
+  <si>
+    <t>0.0009,0.9195,0.9328,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.8479,0.9593,0.0006</t>
+  </si>
+  <si>
+    <t>0.0174,0.5957,0.8699,0.0102</t>
+  </si>
+  <si>
+    <t>0.0145,0.1536,0.9586,0.0022</t>
+  </si>
+  <si>
+    <t>0.0006,0.9198,0.9207,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.6170,0.9220,0.0009</t>
+  </si>
+  <si>
+    <t>0.9941,0.0022,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9818,0.0130,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9763,0.0313,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9783,0.0162,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9911,0.0042,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0052,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9906,0.0033,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9812,0.0207,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0024,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0031,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9956,0.0024,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0012,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0016,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0346,0.0150,0.9561,0.0119</t>
+  </si>
+  <si>
+    <t>0.1628,0.0176,0.8192,0.0416</t>
+  </si>
+  <si>
+    <t>0.8917,0.0044,0.0218,0.0562</t>
+  </si>
+  <si>
+    <t>0.0366,0.0550,0.9229,0.0152</t>
+  </si>
+  <si>
+    <t>0.1362,0.9072,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0082,0.9852,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.1029,0.8944,0.0012,0.0027</t>
+  </si>
+  <si>
+    <t>0.0431,0.9436,0.0009,0.0032</t>
+  </si>
+  <si>
+    <t>0.1484,0.8900,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.0176,0.9780,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.5693,0.6009,0.0058,0.0016</t>
+  </si>
+  <si>
+    <t>0.5082,0.4285,0.1471,0.0266</t>
+  </si>
+  <si>
+    <t>0.3324,0.0385,0.7050,0.0025</t>
+  </si>
+  <si>
+    <t>0.5806,0.0904,0.4108,0.0314</t>
+  </si>
+  <si>
+    <t>0.7742,0.0635,0.1047,0.0472</t>
+  </si>
+  <si>
+    <t>0.0744,0.1656,0.0255,0.9217</t>
+  </si>
+  <si>
+    <t>0.0040,0.9876,0.0101,0.0015</t>
+  </si>
+  <si>
+    <t>0.0015,0.9796,0.0051,0.0617</t>
+  </si>
+  <si>
+    <t>0.0528,0.9066,0.0132,0.0252</t>
+  </si>
+  <si>
+    <t>0.0019,0.9147,0.9291,0.0006</t>
+  </si>
+  <si>
+    <t>0.1091,0.9060,0.0363,0.0004</t>
+  </si>
+  <si>
+    <t>0.6337,0.4132,0.0205,0.0106</t>
+  </si>
+  <si>
+    <t>0.1445,0.8880,0.0061,0.0006</t>
+  </si>
+  <si>
+    <t>0.9858,0.0133,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9777,0.0062,0.0026,0.0048</t>
+  </si>
+  <si>
+    <t>0.9892,0.0012,0.0002,0.0043</t>
+  </si>
+  <si>
+    <t>0.9803,0.0070,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9829,0.0018,0.0002,0.0082</t>
+  </si>
+  <si>
+    <t>0.9864,0.0046,0.0059,0.0011</t>
+  </si>
+  <si>
+    <t>0.9823,0.0117,0.0026,0.0013</t>
+  </si>
+  <si>
+    <t>0.9876,0.0020,0.0012,0.0029</t>
+  </si>
+  <si>
+    <t>0.0011,0.6074,0.9715,0.0003</t>
+  </si>
+  <si>
+    <t>0.0035,0.4524,0.9562,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.2515,0.9611,0.0001</t>
+  </si>
+  <si>
+    <t>0.0759,0.3595,0.6664,0.0174</t>
+  </si>
+  <si>
+    <t>0.5897,0.3112,0.1657,0.0229</t>
+  </si>
+  <si>
+    <t>0.7744,0.0592,0.0856,0.0571</t>
+  </si>
+  <si>
+    <t>0.1325,0.0037,0.9289,0.0090</t>
+  </si>
+  <si>
+    <t>0.4661,0.2086,0.4127,0.0371</t>
+  </si>
+  <si>
+    <t>0.0994,0.0145,0.0012,0.9592</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0017,0.0155,0.0005,0.9984</t>
+  </si>
+  <si>
+    <t>0.0123,0.0003,0.0059,0.9903</t>
+  </si>
+  <si>
+    <t>0.0038,0.8130,0.9095,0.0015</t>
+  </si>
+  <si>
+    <t>0.9812,0.0064,0.0018,0.0021</t>
+  </si>
+  <si>
+    <t>0.5186,0.4882,0.0015,0.0119</t>
+  </si>
+  <si>
+    <t>0.9771,0.0116,0.0050,0.0019</t>
+  </si>
+  <si>
+    <t>0.6452,0.4959,0.0090,0.0026</t>
+  </si>
+  <si>
+    <t>0.9783,0.0039,0.0017,0.0059</t>
+  </si>
+  <si>
+    <t>0.7395,0.0141,0.0401,0.2285</t>
+  </si>
+  <si>
+    <t>0.9643,0.0179,0.0030,0.0052</t>
+  </si>
+  <si>
+    <t>0.0076,0.2737,0.9524,0.0109</t>
+  </si>
+  <si>
+    <t>0.8981,0.0006,0.0112,0.0720</t>
+  </si>
+  <si>
+    <t>0.9117,0.0052,0.0224,0.0369</t>
+  </si>
+  <si>
+    <t>0.2695,0.7565,0.0111,0.0096</t>
+  </si>
+  <si>
+    <t>0.7236,0.3049,0.0078,0.0135</t>
+  </si>
+  <si>
+    <t>0.8450,0.1546,0.0159,0.0049</t>
+  </si>
+  <si>
+    <t>0.0931,0.8900,0.0042,0.0103</t>
+  </si>
+  <si>
+    <t>0.6980,0.2701,0.0738,0.0123</t>
+  </si>
+  <si>
+    <t>0.8301,0.1443,0.0535,0.0085</t>
+  </si>
+  <si>
+    <t>0.9902,0.0025,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9824,0.0093,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.9924,0.0036,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9891,0.0011,0.0011,0.0041</t>
+  </si>
+  <si>
+    <t>0.9894,0.0030,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9894,0.0033,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9885,0.0014,0.0003,0.0038</t>
+  </si>
+  <si>
+    <t>0.9931,0.0017,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.2588,0.8247,0.0071,0.0023</t>
+  </si>
+  <si>
+    <t>0.4742,0.6625,0.0068,0.0008</t>
+  </si>
+  <si>
+    <t>0.3163,0.6982,0.0410,0.0008</t>
+  </si>
+  <si>
+    <t>0.7080,0.2464,0.0932,0.0019</t>
+  </si>
+  <si>
+    <t>0.9513,0.0721,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9661,0.0189,0.0085,0.0026</t>
+  </si>
+  <si>
+    <t>0.9814,0.0144,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9212,0.0745,0.0138,0.0029</t>
+  </si>
+  <si>
+    <t>0.0019,0.0168,0.9951,0.0011</t>
+  </si>
+  <si>
+    <t>0.9255,0.0891,0.0036,0.0028</t>
+  </si>
+  <si>
+    <t>0.0046,0.0248,0.9850,0.0005</t>
+  </si>
+  <si>
+    <t>0.0102,0.2283,0.9564,0.0093</t>
+  </si>
+  <si>
+    <t>0.0074,0.0009,0.9855,0.0174</t>
+  </si>
+  <si>
+    <t>0.0141,0.0368,0.9542,0.0150</t>
+  </si>
+  <si>
+    <t>0.0239,0.0354,0.9500,0.0034</t>
+  </si>
+  <si>
+    <t>0.0037,0.0013,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.0027,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.1235,0.0498,0.8175,0.0773</t>
+  </si>
+  <si>
+    <t>0.1248,0.0147,0.8984,0.0212</t>
+  </si>
+  <si>
+    <t>0.5263,0.0181,0.6082,0.0159</t>
+  </si>
+  <si>
+    <t>0.2265,0.0685,0.7648,0.0054</t>
+  </si>
+  <si>
+    <t>0.1034,0.7302,0.2843,0.0030</t>
+  </si>
+  <si>
+    <t>0.6441,0.1758,0.2133,0.0323</t>
+  </si>
+  <si>
+    <t>0.6457,0.2156,0.2072,0.0120</t>
+  </si>
+  <si>
+    <t>0.2130,0.0286,0.8328,0.0071</t>
+  </si>
+  <si>
+    <t>0.7136,0.4502,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.5644,0.5633,0.0056,0.0010</t>
+  </si>
+  <si>
+    <t>0.9444,0.0722,0.0061,0.0009</t>
+  </si>
+  <si>
+    <t>0.9513,0.0676,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.9662,0.0370,0.0026,0.0012</t>
+  </si>
+  <si>
+    <t>0.3423,0.2842,0.3668,0.0131</t>
+  </si>
+  <si>
+    <t>0.8170,0.0044,0.2218,0.0157</t>
+  </si>
+  <si>
+    <t>0.6289,0.0693,0.1168,0.2803</t>
+  </si>
+  <si>
+    <t>0.7583,0.0108,0.4066,0.0029</t>
+  </si>
+  <si>
+    <t>0.7902,0.0112,0.2653,0.0148</t>
+  </si>
+  <si>
+    <t>0.0122,0.0271,0.9498,0.0544</t>
+  </si>
+  <si>
+    <t>0.0518,0.3248,0.7507,0.0570</t>
+  </si>
+  <si>
+    <t>0.0094,0.0641,0.9766,0.0006</t>
+  </si>
+  <si>
+    <t>0.0044,0.0111,0.9873,0.0030</t>
+  </si>
+  <si>
+    <t>0.0567,0.2627,0.8286,0.0055</t>
+  </si>
+  <si>
+    <t>0.9831,0.0104,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9867,0.0097,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9905,0.0086,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9948,0.0023,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9896,0.0064,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9880,0.0141,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0020,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9881,0.0034,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.0214,0.0144,0.9704,0.0096</t>
+  </si>
+  <si>
+    <t>0.1255,0.3386,0.6090,0.0045</t>
+  </si>
+  <si>
+    <t>0.9267,0.0199,0.0074,0.0276</t>
+  </si>
+  <si>
+    <t>0.0121,0.0088,0.9819,0.0014</t>
+  </si>
+  <si>
+    <t>0.0017,0.0041,0.9915,0.0041</t>
+  </si>
+  <si>
+    <t>0.0018,0.0486,0.9872,0.0010</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9974,0.0018</t>
+  </si>
+  <si>
+    <t>0.0275,0.1655,0.8157,0.0124</t>
+  </si>
+  <si>
+    <t>0.0004,0.0045,0.9964,0.0038</t>
+  </si>
+  <si>
+    <t>0.0265,0.0367,0.8935,0.0747</t>
+  </si>
+  <si>
+    <t>0.0207,0.1108,0.9230,0.0020</t>
+  </si>
+  <si>
+    <t>0.7741,0.0328,0.2559,0.0137</t>
+  </si>
+  <si>
+    <t>0.6553,0.0008,0.3055,0.0320</t>
+  </si>
+  <si>
+    <t>0.9304,0.0023,0.0472,0.0091</t>
+  </si>
+  <si>
+    <t>0.9944,0.0028,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0018,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9935,0.0038,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9889,0.0103,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9877,0.0022,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9931,0.0047,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9923,0.0032,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9945,0.0015,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0034,0.2847,0.9389,0.0004</t>
+  </si>
+  <si>
+    <t>0.0654,0.0573,0.9037,0.0144</t>
+  </si>
+  <si>
+    <t>0.0423,0.4723,0.7195,0.0090</t>
+  </si>
+  <si>
+    <t>0.0496,0.1163,0.8106,0.0099</t>
+  </si>
+  <si>
+    <t>0.0074,0.0030,0.9887,0.0016</t>
+  </si>
+  <si>
+    <t>0.0574,0.0025,0.8625,0.1225</t>
+  </si>
+  <si>
+    <t>0.0404,0.0046,0.9688,0.0024</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9732,0.2158</t>
+  </si>
+  <si>
+    <t>0.8396,0.0018,0.0087,0.1864</t>
+  </si>
+  <si>
+    <t>0.0661,0.1925,0.0049,0.9211</t>
+  </si>
+  <si>
+    <t>0.0341,0.0037,0.0195,0.9712</t>
+  </si>
+  <si>
+    <t>0.0108,0.0005,0.0027,0.9929</t>
+  </si>
+  <si>
+    <t>0.0020,0.0011,0.0016,0.9982</t>
+  </si>
+  <si>
+    <t>0.8150,0.0848,0.0229,0.0555</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
